--- a/gemini-2.0-flash.xlsx
+++ b/gemini-2.0-flash.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3548,6 +3548,3801 @@
         </is>
       </c>
       <c r="AG19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>At about 19151 on 7 October 2022</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>North Atlantic, approximately 150nm west of Ireland</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>After making “Mayday” calls and activating the Digital Selective Calling (DSC)2 alarm at about 1935</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>North Atlantic, approximately 150nm west of Ireland</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>No, the first communication was after the incident.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>20 crew: a Spanish master, mate, chief engineer and bosun and 16 Indonesian nationals.</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Eder Sands was approximately 150nm west of Ireland on a southerly heading at about 5 knots (kts) when the crew laid an anchor weight and marker buoys and began to shoot a gill net.</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1/2024</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fatal fall overboard from the fishing vessel Eder Sands (UL 257) approximately 150 nautical miles west of Ireland on 7 October 2022</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>North Atlantic, approximately 150nm west of Ireland</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>“Mayday” calls and activating the Digital Selective Calling (DSC) alarm at about 1935</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>North Atlantic, approximately 150nm west of Ireland</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>The skipper used astern power to stop the vessel and sounded the crew alarm and whistle.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>20 crew: a Spanish master, mate, chief engineer and bosun and 16 Indonesian nationals.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Harriet J</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AH180</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Creel fishing vessel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Glass reinforced plastic</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>St Abbs</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>St Abbs (intended)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Very Serious Marine Casualty</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2nm west o</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>the gear on the deck of Harriet J</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>a chain weight in his fishing gear</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>the effects of cold incapacitation</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>the fourth fleet of creels</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PFD</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>drowning</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Yes, a notable dip in speed</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Approximately 3 hours</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0.9nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Harriet J</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AH180</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Creel fishing vessel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Glass reinforced plastic</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>St Abbs</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>St Abbs (intended)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Very Serious Marine Casualty</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2nm west of Fast Castle Head</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>gear on the deck of Harriet J</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>cold incapacitation</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26 July 2022</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1 October 2019</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MSN 1871 (F) – The Code of Practice for the Safety of Small Fishing Vessels of less than 15m Length Overall</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>local fishermen’s association or had registered with the SafetyFolder service</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>the Home and Dry safety campaign</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Yes, a notable dip in speed while shooting the fourth fleet</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0.9nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Harriet J</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AH180</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Creel fishing vessel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Glass reinforced plastic</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7.19m</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>St Abbs</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>St Abbs (intended)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Very Serious Marine Casualty</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2nm west o</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1.2m</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>12°C</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>15°C</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>0656</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>0.6kts</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>gear on the deck of Harriet J</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2, Emma Louise’s owner, William Traynor, and The owner’s brother-in-law, Martin Steventon</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Over the past 10 years the MAIB has investigated five accidents involving CO poisoning on pleasure vessels that (including this one) resulted in the tragic loss of nine lives.</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2, Emma Louise’s owner, William Traynor, and the owner’s brother-in-law, Martin Steventon</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2 fatalities</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Light northerly wind; drizzle; 10°C</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>each drank a bee r</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>three crew: skipper, senior deckhand, junior deckhand</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ronja Harvester</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>adverse weather</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>standing on the net, attempting to bring it back on board</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Mallaig ALB</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>foredeck of Reul A Chuain</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>At 1906, the junior deckhand made a distress call on very high frequency channel 16, which was immediately answered by the coastguard.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>The skipper had talked him through emergency scenarios during his time on board, his focus was on operating the fishing gear.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Yes, reduced speed to neutral</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24 June 2021</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>the fishing vessel Reul A Chuain (OB915)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>in the Sound of Rùm, Scotland</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VERY SERIOUS MARINE CASUALTY REPORT NO 14/20 22</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DECEMBER 2022</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Accident Reporting and Investigation) Regulations 2012</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>not written with litigation in mind</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>the prevention of future accidents</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>www.gov.uk/maib</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>on passage with three crew to Mallaig, Scotland</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Lachlan Robertson died from the effects of immersion in water</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>The MAIB has issued a safety flyer to the fishing industry, summarising advice provided in MCA publications.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>safety harness or lifelines being present on board</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Reul A</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>perform CPR</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>risk assessments had not been updated for some time and several risk mitigation measures were not routinely applied by the crew once the vessel was at sea</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>was an emergency situation</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>slipped out</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>crew were provided with restraint arrangements as adequate protection</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>lifelines and safety belts shall be provided</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>three crew, The skipper, senior deckhand, and junior deckhand</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Ronja Harvester</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Yes, approximately 7.69%</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Previous inspections had revealed numerous deficiencies that required rectification by the owner</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Previous inspections had revealed numerous deficiencies that required rectification by the owner</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>in the approaches to Lynmouth, England</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Daylight; wind north-westerly force 3; wave height 0.5m-1.0m</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>"Mayday!" call using the hand-held very high frequency (VHF) radio</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>No response was heard to the VHF “Mayday!” call</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>the skipper’s safety brief to the crew member before they departed and the wearing of PFDs ensured that the abandonment was safely executed</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2, the skipper and a crew member</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>At a speed of about 5 knots</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>approximately 30 minutes</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>in the approaches to Lynmouth, England</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Daylight; wind north-westerly force 3; wave height 0.5m-1.0m</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>“Mayday!” call</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>No response was heard to the VHF “Mayday!” call</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>skipper’s safety brief to the crew member before they departed and the wearing of PFDs ensured that the abandonment was safely executed</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2, the skipper and a crew member</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Bella’s heading to the north-west (Figure 2) into sea at a speed of about 5 knots</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Approximately 30 minutes</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Saint Peter (LH22)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2 May 2021, between 0800 and1000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>east of Torness Point, Scotland</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>The winchman recovered the skipper to the helicopter and its crew cut away his PFD so that emergency first aid could be carried out during the flight to the Royal Infirmary of Edi</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>An EPIRB transmits a 406 megahertz (MHz) distress signal via satellite to the coastguard</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>The wheelhouse throttle control was not operational, and the vessel could only be driven by the controls next to the hauling table.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>shooting creels</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>the owner/skipper (the skipper)</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MAIB has issued a safety flyer to the fishing industry highlighting the lessons to be learned from this accident.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.safetyfolder.co.uk/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ischaemic and hypertensive heart disease and immersion in water</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hypertensive</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DSC capability</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>The wheelhouse throttle control was not operational, and the vessel could only be driven by the controls next to the hauling table.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>shooting creels</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>the owner/skipper (the skipper)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>bulk carrier anchored off Tynemouth, 1nm away from the accident position</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Minor indentation to hull port side near frame 45, bent handrails/none</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Sprung hull planks at stem above and below waterline</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>In passage</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>In passage</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>General cargo</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Trawler</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>81.78</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>9.93</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Red Stone in bulk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>restricted visibility</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Red Stone in bulk</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>A bulk carrier anchored off Tynemouth, 1nm away from the accident position</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Minor indentation to hull port side near frame 45, bent handrails/none</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Sprung hull planks at stem above and below waterline</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>In passage</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>In passage</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Achieve (HL257) and general cargo ship Talis</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Neither crew was keeping an effective lookout in the prevailing conditions of restricted visibility</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Action taken by Talis’s C/O was too late</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Red Stone in bulk</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>restricted visibility</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Red Stone in bulk</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Three; Globetrotter’s owner, his son, and a friend</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No; -</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Yes; -</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>31 May 2020</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>The owner raised a “Mayday”</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>two lifebuoys</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>a catastrophic failure of the boat’s hull</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>•Globetrotter most likely sank due to flooding caused by catastrophic hull failure or damage to the rudder stock.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>at a rate of about 0.6 knot</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>15.3°C</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>“off Bispham”</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Fleetwood Royal National Lifeboat Institution (RNLI) inshore lifeboat</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>in the forward cabin, on a hook inside the wheelhouse door, by the cabin door</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Globetrotter ’s owner contacted Fivebuoys ’ skipper by mobile telephone</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>three men on board: Globetrotter’s owner, his son and friend</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No. CCTV footage showed the vessels did not follow the same track.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Yes, Pisces was in sight of Globetrotter.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>the exact cause of the water ingress that led to the foundering of Globetrotter</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>failure of the boat’s hull</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>the boat grounding on a sand bank during itspassage out to sea</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>floodi</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Globetrotter</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Globetrotter</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0724</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>easterly Beaufort force 3 to 4</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>about 0.6 knot, and the sea water temperature was 15.3°C</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>a bucket</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>forward cabin; wheelhouse door</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Loch Alsh</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>the wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>stepped through the open gate and on to the barge access ladder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Polarcirkel rigid buoyancy boats (RBB)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>the vertical fender on the right-hand side of the ladder was missing after becoming detached following a heavy contact during a feed delivery on 8 February 2020</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>The conduct of regular emergency drills helps ensure that all crew members are familiar with their vessel’s emergency procedures and safety equipment and are therefore fully prepared to respond when things go wrong.</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Beinn Na Caillich ’s skipper engaged astern propulsion to slow the vessel</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>the wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>eat his lunch</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Polarcirkel rigid buoyancy boats (RBB)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>The health and safety team monitored the certification and training of the workboat crews.</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Beinn Na Caillich ’s skipper engaged astern propulsion to slow the vessel as it approached the barge</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Seadogz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>up to 20 miles from a safe haven, in favourable weather and in daylight</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Category 4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>overcast with bright spells, West-south-westerly winds, force 4-5, slight seas, good visibility</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>concentrating on conducting high speed manoeuvres in close proximity to another vessel</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>12; 2 crew + 12 passengers</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gemini-2.0-flash</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Seadogz</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Extreme RIB Experiences , Treasure Hunts , Corporate Team Building Events, and trips for Stag and Hen parties</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Red Bay Ribs Ltd in 2012</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2 x 300 HP Yahama outboards</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ad-hoc basis for over 8 years</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>concentrating on conducting high speed manoeuvres in close proximity to another vessel and did not see the fixed navigational mark in time to take avoiding action</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>12; 2 crew + 12 passengers</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
